--- a/artfynd/A 15738-2025 artfynd.xlsx
+++ b/artfynd/A 15738-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129195311</v>
+        <v>129195335</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>88926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442561</v>
+        <v>442874</v>
       </c>
       <c r="R2" t="n">
-        <v>6777001</v>
+        <v>6777100</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129195301</v>
+        <v>129195311</v>
       </c>
       <c r="B3" t="n">
         <v>57720</v>
@@ -813,7 +809,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -823,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442670</v>
+        <v>442561</v>
       </c>
       <c r="R3" t="n">
-        <v>6777068</v>
+        <v>6777001</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +881,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129195302</v>
+        <v>129195301</v>
       </c>
       <c r="B4" t="n">
         <v>57720</v>
@@ -928,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442712</v>
+        <v>442670</v>
       </c>
       <c r="R4" t="n">
-        <v>6777097</v>
+        <v>6777068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129195335</v>
+        <v>129195302</v>
       </c>
       <c r="B5" t="n">
-        <v>88926</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,26 +997,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1028,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442874</v>
+        <v>442712</v>
       </c>
       <c r="R5" t="n">
-        <v>6777100</v>
+        <v>6777097</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1073,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1390,37 +1390,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129195331</v>
+        <v>129195309</v>
       </c>
       <c r="B9" t="n">
-        <v>92819</v>
+        <v>57720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1428,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442474</v>
+        <v>442643</v>
       </c>
       <c r="R9" t="n">
-        <v>6776957</v>
+        <v>6777058</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1477,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,7 +1495,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129195309</v>
+        <v>129195303</v>
       </c>
       <c r="B10" t="n">
         <v>57720</v>
@@ -1534,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442643</v>
+        <v>442807</v>
       </c>
       <c r="R10" t="n">
-        <v>6777058</v>
+        <v>6777118</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,7 +1600,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129195303</v>
+        <v>129195306</v>
       </c>
       <c r="B11" t="n">
         <v>57720</v>
@@ -1639,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442807</v>
+        <v>442828</v>
       </c>
       <c r="R11" t="n">
-        <v>6777118</v>
+        <v>6777062</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,42 +1705,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129195306</v>
+        <v>129195331</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>92819</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1744,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442828</v>
+        <v>442474</v>
       </c>
       <c r="R12" t="n">
-        <v>6777062</v>
+        <v>6776957</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,6 +1787,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -3523,45 +3523,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129195325</v>
+        <v>129195333</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442637</v>
+        <v>442570</v>
       </c>
       <c r="R30" t="n">
-        <v>6777062</v>
+        <v>6776989</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3602,6 +3605,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3620,48 +3624,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129195333</v>
+        <v>129195325</v>
       </c>
       <c r="B31" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442570</v>
+        <v>442637</v>
       </c>
       <c r="R31" t="n">
-        <v>6776989</v>
+        <v>6777062</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,7 +3703,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15738-2025 artfynd.xlsx
+++ b/artfynd/A 15738-2025 artfynd.xlsx
@@ -1390,42 +1390,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129195309</v>
+        <v>129195331</v>
       </c>
       <c r="B9" t="n">
-        <v>57720</v>
+        <v>92819</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1433,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442643</v>
+        <v>442474</v>
       </c>
       <c r="R9" t="n">
-        <v>6777058</v>
+        <v>6776957</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,6 +1472,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1495,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129195303</v>
+        <v>129195309</v>
       </c>
       <c r="B10" t="n">
         <v>57720</v>
@@ -1538,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442807</v>
+        <v>442643</v>
       </c>
       <c r="R10" t="n">
-        <v>6777118</v>
+        <v>6777058</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,7 +1596,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129195306</v>
+        <v>129195303</v>
       </c>
       <c r="B11" t="n">
         <v>57720</v>
@@ -1643,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442828</v>
+        <v>442807</v>
       </c>
       <c r="R11" t="n">
-        <v>6777062</v>
+        <v>6777118</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,37 +1701,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129195331</v>
+        <v>129195306</v>
       </c>
       <c r="B12" t="n">
-        <v>92819</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1743,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442474</v>
+        <v>442828</v>
       </c>
       <c r="R12" t="n">
-        <v>6776957</v>
+        <v>6777062</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,7 +1788,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -3523,48 +3523,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129195333</v>
+        <v>129195325</v>
       </c>
       <c r="B30" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442570</v>
+        <v>442637</v>
       </c>
       <c r="R30" t="n">
-        <v>6776989</v>
+        <v>6777062</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3605,7 +3602,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3624,45 +3620,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129195325</v>
+        <v>129195333</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442637</v>
+        <v>442570</v>
       </c>
       <c r="R31" t="n">
-        <v>6777062</v>
+        <v>6776989</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3703,6 +3702,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15738-2025 artfynd.xlsx
+++ b/artfynd/A 15738-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129195335</v>
+        <v>129195301</v>
       </c>
       <c r="B2" t="n">
-        <v>88926</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442874</v>
+        <v>442670</v>
       </c>
       <c r="R2" t="n">
-        <v>6777100</v>
+        <v>6777068</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,7 +762,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -881,7 +885,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129195301</v>
+        <v>129195302</v>
       </c>
       <c r="B4" t="n">
         <v>57720</v>
@@ -924,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442670</v>
+        <v>442712</v>
       </c>
       <c r="R4" t="n">
-        <v>6777068</v>
+        <v>6777097</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129195302</v>
+        <v>129195335</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>88926</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,31 +1001,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1029,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442712</v>
+        <v>442874</v>
       </c>
       <c r="R5" t="n">
-        <v>6777097</v>
+        <v>6777100</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,6 +1072,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1903,45 +1903,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129195321</v>
+        <v>129195336</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>5177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442695</v>
+        <v>442750</v>
       </c>
       <c r="R14" t="n">
-        <v>6777083</v>
+        <v>6777113</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1982,6 +1991,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2000,54 +2010,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129195336</v>
+        <v>129195321</v>
       </c>
       <c r="B15" t="n">
-        <v>5177</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442750</v>
+        <v>442695</v>
       </c>
       <c r="R15" t="n">
-        <v>6777113</v>
+        <v>6777083</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,7 +2089,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129195298</v>
+        <v>129195312</v>
       </c>
       <c r="B25" t="n">
-        <v>57883</v>
+        <v>57720</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,21 +3017,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442628</v>
+        <v>442510</v>
       </c>
       <c r="R25" t="n">
-        <v>6777045</v>
+        <v>6776988</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129195312</v>
+        <v>129195308</v>
       </c>
       <c r="B26" t="n">
         <v>57720</v>
@@ -3144,7 +3144,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442510</v>
+        <v>442733</v>
       </c>
       <c r="R26" t="n">
-        <v>6776988</v>
+        <v>6777012</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129195308</v>
+        <v>129195298</v>
       </c>
       <c r="B27" t="n">
-        <v>57720</v>
+        <v>57883</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3249,7 +3249,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442733</v>
+        <v>442628</v>
       </c>
       <c r="R27" t="n">
-        <v>6777012</v>
+        <v>6777045</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3523,45 +3523,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129195325</v>
+        <v>129195333</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442637</v>
+        <v>442570</v>
       </c>
       <c r="R30" t="n">
-        <v>6777062</v>
+        <v>6776989</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3602,6 +3605,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3620,48 +3624,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129195333</v>
+        <v>129195325</v>
       </c>
       <c r="B31" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442570</v>
+        <v>442637</v>
       </c>
       <c r="R31" t="n">
-        <v>6776989</v>
+        <v>6777062</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3702,7 +3703,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15738-2025 artfynd.xlsx
+++ b/artfynd/A 15738-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129195301</v>
+        <v>129195311</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442670</v>
+        <v>442561</v>
       </c>
       <c r="R2" t="n">
-        <v>6777068</v>
+        <v>6777001</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129195311</v>
+        <v>129195301</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442561</v>
+        <v>442670</v>
       </c>
       <c r="R3" t="n">
-        <v>6777001</v>
+        <v>6777068</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +888,7 @@
         <v>129195302</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>129195335</v>
       </c>
       <c r="B5" t="n">
-        <v>88926</v>
+        <v>88930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129195334</v>
       </c>
       <c r="B6" t="n">
-        <v>88926</v>
+        <v>88930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>129195319</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>129195296</v>
       </c>
       <c r="B8" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>129195331</v>
       </c>
       <c r="B9" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>129195309</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>129195303</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>129195306</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129195294</v>
+        <v>129195321</v>
       </c>
       <c r="B13" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1817,21 +1817,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442435</v>
+        <v>442695</v>
       </c>
       <c r="R13" t="n">
-        <v>6776960</v>
+        <v>6777083</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129195321</v>
+        <v>129195294</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,21 +2021,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442695</v>
+        <v>442435</v>
       </c>
       <c r="R15" t="n">
-        <v>6777083</v>
+        <v>6776960</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2217,7 +2217,7 @@
         <v>129195329</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>129195322</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>129195307</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>129195310</v>
       </c>
       <c r="B20" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>129195327</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>129195330</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>129195320</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>129195324</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>129195312</v>
       </c>
       <c r="B25" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>129195308</v>
       </c>
       <c r="B26" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>129195298</v>
       </c>
       <c r="B27" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>129195326</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>129195313</v>
       </c>
       <c r="B29" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>129195333</v>
       </c>
       <c r="B30" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>129195325</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>129195332</v>
       </c>
       <c r="B32" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>129195328</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 15738-2025 artfynd.xlsx
+++ b/artfynd/A 15738-2025 artfynd.xlsx
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129195296</v>
+        <v>129195309</v>
       </c>
       <c r="B8" t="n">
-        <v>91533</v>
+        <v>57722</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,26 +1300,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442804</v>
+        <v>442643</v>
       </c>
       <c r="R8" t="n">
-        <v>6777066</v>
+        <v>6777058</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,7 +1376,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1390,37 +1394,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129195331</v>
+        <v>129195303</v>
       </c>
       <c r="B9" t="n">
-        <v>92826</v>
+        <v>57722</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1428,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442474</v>
+        <v>442807</v>
       </c>
       <c r="R9" t="n">
-        <v>6776957</v>
+        <v>6777118</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1481,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,7 +1499,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129195309</v>
+        <v>129195306</v>
       </c>
       <c r="B10" t="n">
         <v>57722</v>
@@ -1534,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442643</v>
+        <v>442828</v>
       </c>
       <c r="R10" t="n">
-        <v>6777058</v>
+        <v>6777062</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129195303</v>
+        <v>129195296</v>
       </c>
       <c r="B11" t="n">
-        <v>57722</v>
+        <v>91533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1607,31 +1615,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1639,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442807</v>
+        <v>442804</v>
       </c>
       <c r="R11" t="n">
-        <v>6777118</v>
+        <v>6777066</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,6 +1686,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1701,42 +1705,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129195306</v>
+        <v>129195331</v>
       </c>
       <c r="B12" t="n">
-        <v>57722</v>
+        <v>92826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1744,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442828</v>
+        <v>442474</v>
       </c>
       <c r="R12" t="n">
-        <v>6777062</v>
+        <v>6776957</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,6 +1787,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129195312</v>
+        <v>129195298</v>
       </c>
       <c r="B25" t="n">
-        <v>57722</v>
+        <v>57885</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,21 +3017,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442510</v>
+        <v>442628</v>
       </c>
       <c r="R25" t="n">
-        <v>6776988</v>
+        <v>6777045</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129195308</v>
+        <v>129195312</v>
       </c>
       <c r="B26" t="n">
         <v>57722</v>
@@ -3144,7 +3144,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442733</v>
+        <v>442510</v>
       </c>
       <c r="R26" t="n">
-        <v>6777012</v>
+        <v>6776988</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129195298</v>
+        <v>129195308</v>
       </c>
       <c r="B27" t="n">
-        <v>57885</v>
+        <v>57722</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3249,7 +3249,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442628</v>
+        <v>442733</v>
       </c>
       <c r="R27" t="n">
-        <v>6777045</v>
+        <v>6777012</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 15738-2025 artfynd.xlsx
+++ b/artfynd/A 15738-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129195311</v>
+        <v>129195335</v>
       </c>
       <c r="B2" t="n">
-        <v>57722</v>
+        <v>88937</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442561</v>
+        <v>442874</v>
       </c>
       <c r="R2" t="n">
-        <v>6777001</v>
+        <v>6777100</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,6 +757,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -780,7 +776,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129195301</v>
+        <v>129195311</v>
       </c>
       <c r="B3" t="n">
         <v>57722</v>
@@ -813,7 +809,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -823,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442670</v>
+        <v>442561</v>
       </c>
       <c r="R3" t="n">
-        <v>6777068</v>
+        <v>6777001</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +881,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129195302</v>
+        <v>129195301</v>
       </c>
       <c r="B4" t="n">
         <v>57722</v>
@@ -928,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442712</v>
+        <v>442670</v>
       </c>
       <c r="R4" t="n">
-        <v>6777097</v>
+        <v>6777068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129195335</v>
+        <v>129195302</v>
       </c>
       <c r="B5" t="n">
-        <v>88930</v>
+        <v>57722</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,26 +997,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1028,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442874</v>
+        <v>442712</v>
       </c>
       <c r="R5" t="n">
-        <v>6777100</v>
+        <v>6777097</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,7 +1073,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1094,7 +1094,7 @@
         <v>129195334</v>
       </c>
       <c r="B6" t="n">
-        <v>88930</v>
+        <v>88937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,42 +1289,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129195309</v>
+        <v>129195331</v>
       </c>
       <c r="B8" t="n">
-        <v>57722</v>
+        <v>92833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442643</v>
+        <v>442474</v>
       </c>
       <c r="R8" t="n">
-        <v>6777058</v>
+        <v>6776957</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1376,6 +1371,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1394,7 +1390,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129195303</v>
+        <v>129195309</v>
       </c>
       <c r="B9" t="n">
         <v>57722</v>
@@ -1437,10 +1433,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442807</v>
+        <v>442643</v>
       </c>
       <c r="R9" t="n">
-        <v>6777118</v>
+        <v>6777058</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1495,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129195306</v>
+        <v>129195303</v>
       </c>
       <c r="B10" t="n">
         <v>57722</v>
@@ -1542,10 +1538,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442828</v>
+        <v>442807</v>
       </c>
       <c r="R10" t="n">
-        <v>6777062</v>
+        <v>6777118</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,10 +1600,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129195296</v>
+        <v>129195306</v>
       </c>
       <c r="B11" t="n">
-        <v>91533</v>
+        <v>57722</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1615,26 +1611,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1642,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442804</v>
+        <v>442828</v>
       </c>
       <c r="R11" t="n">
-        <v>6777066</v>
+        <v>6777062</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,7 +1687,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1705,32 +1705,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129195331</v>
+        <v>129195296</v>
       </c>
       <c r="B12" t="n">
-        <v>92826</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442474</v>
+        <v>442804</v>
       </c>
       <c r="R12" t="n">
-        <v>6776957</v>
+        <v>6777066</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,54 +1903,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129195336</v>
+        <v>129195294</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>79658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442750</v>
+        <v>442435</v>
       </c>
       <c r="R14" t="n">
-        <v>6777113</v>
+        <v>6776960</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1991,7 +1982,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2010,45 +2000,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129195294</v>
+        <v>129195336</v>
       </c>
       <c r="B15" t="n">
-        <v>79658</v>
+        <v>5177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442435</v>
+        <v>442750</v>
       </c>
       <c r="R15" t="n">
-        <v>6776960</v>
+        <v>6777113</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,6 +2088,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129195298</v>
+        <v>129195312</v>
       </c>
       <c r="B25" t="n">
-        <v>57885</v>
+        <v>57722</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,21 +3017,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442628</v>
+        <v>442510</v>
       </c>
       <c r="R25" t="n">
-        <v>6777045</v>
+        <v>6776988</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129195312</v>
+        <v>129195308</v>
       </c>
       <c r="B26" t="n">
         <v>57722</v>
@@ -3144,7 +3144,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442510</v>
+        <v>442733</v>
       </c>
       <c r="R26" t="n">
-        <v>6776988</v>
+        <v>6777012</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129195308</v>
+        <v>129195298</v>
       </c>
       <c r="B27" t="n">
-        <v>57722</v>
+        <v>57885</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3249,7 +3249,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442733</v>
+        <v>442628</v>
       </c>
       <c r="R27" t="n">
-        <v>6777012</v>
+        <v>6777045</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,7 +3526,7 @@
         <v>129195333</v>
       </c>
       <c r="B30" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>129195332</v>
       </c>
       <c r="B32" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 15738-2025 artfynd.xlsx
+++ b/artfynd/A 15738-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129195335</v>
       </c>
       <c r="B2" t="n">
-        <v>88937</v>
+        <v>88939</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>129195311</v>
       </c>
       <c r="B3" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
         <v>129195301</v>
       </c>
       <c r="B4" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>129195302</v>
       </c>
       <c r="B5" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129195334</v>
       </c>
       <c r="B6" t="n">
-        <v>88937</v>
+        <v>88939</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>129195319</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129195331</v>
+        <v>129195296</v>
       </c>
       <c r="B8" t="n">
-        <v>92833</v>
+        <v>91542</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442474</v>
+        <v>442804</v>
       </c>
       <c r="R8" t="n">
-        <v>6776957</v>
+        <v>6777066</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,42 +1390,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129195309</v>
+        <v>129195331</v>
       </c>
       <c r="B9" t="n">
-        <v>57722</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1433,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442643</v>
+        <v>442474</v>
       </c>
       <c r="R9" t="n">
-        <v>6777058</v>
+        <v>6776957</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1477,6 +1472,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1495,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129195303</v>
+        <v>129195309</v>
       </c>
       <c r="B10" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1538,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442807</v>
+        <v>442643</v>
       </c>
       <c r="R10" t="n">
-        <v>6777118</v>
+        <v>6777058</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,10 +1596,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129195306</v>
+        <v>129195303</v>
       </c>
       <c r="B11" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1643,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442828</v>
+        <v>442807</v>
       </c>
       <c r="R11" t="n">
-        <v>6777062</v>
+        <v>6777118</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1701,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129195296</v>
+        <v>129195306</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,26 +1712,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1743,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442804</v>
+        <v>442828</v>
       </c>
       <c r="R12" t="n">
-        <v>6777066</v>
+        <v>6777062</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,7 +1788,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>129195321</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>129195294</v>
       </c>
       <c r="B14" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         <v>129195329</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>129195322</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>129195307</v>
       </c>
       <c r="B19" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>129195310</v>
       </c>
       <c r="B20" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>129195327</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>129195330</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>129195320</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>129195324</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>129195312</v>
       </c>
       <c r="B25" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>129195308</v>
       </c>
       <c r="B26" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
         <v>129195298</v>
       </c>
       <c r="B27" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>129195326</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>129195313</v>
       </c>
       <c r="B29" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>129195333</v>
       </c>
       <c r="B30" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>129195325</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>129195332</v>
       </c>
       <c r="B32" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>129195328</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 15738-2025 artfynd.xlsx
+++ b/artfynd/A 15738-2025 artfynd.xlsx
@@ -1806,45 +1806,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129195321</v>
+        <v>129195336</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>5177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442695</v>
+        <v>442750</v>
       </c>
       <c r="R13" t="n">
-        <v>6777083</v>
+        <v>6777113</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,6 +1894,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1903,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129195294</v>
+        <v>129195321</v>
       </c>
       <c r="B14" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1914,21 +1924,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1938,10 +1948,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442435</v>
+        <v>442695</v>
       </c>
       <c r="R14" t="n">
-        <v>6776960</v>
+        <v>6777083</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,54 +2010,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129195336</v>
+        <v>129195294</v>
       </c>
       <c r="B15" t="n">
-        <v>5177</v>
+        <v>79660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442750</v>
+        <v>442435</v>
       </c>
       <c r="R15" t="n">
-        <v>6777113</v>
+        <v>6776960</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2088,7 +2089,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 15738-2025 artfynd.xlsx
+++ b/artfynd/A 15738-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129195335</v>
       </c>
       <c r="B2" t="n">
-        <v>88939</v>
+        <v>88940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129195334</v>
       </c>
       <c r="B6" t="n">
-        <v>88939</v>
+        <v>88940</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129195296</v>
+        <v>129195309</v>
       </c>
       <c r="B8" t="n">
-        <v>91542</v>
+        <v>57724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,26 +1300,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442804</v>
+        <v>442643</v>
       </c>
       <c r="R8" t="n">
-        <v>6777066</v>
+        <v>6777058</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,7 +1376,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1390,37 +1394,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129195331</v>
+        <v>129195303</v>
       </c>
       <c r="B9" t="n">
-        <v>92835</v>
+        <v>57724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1428,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442474</v>
+        <v>442807</v>
       </c>
       <c r="R9" t="n">
-        <v>6776957</v>
+        <v>6777118</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1481,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,7 +1499,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129195309</v>
+        <v>129195306</v>
       </c>
       <c r="B10" t="n">
         <v>57724</v>
@@ -1534,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442643</v>
+        <v>442828</v>
       </c>
       <c r="R10" t="n">
-        <v>6777058</v>
+        <v>6777062</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,42 +1604,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129195303</v>
+        <v>129195331</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>92821</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1639,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442807</v>
+        <v>442474</v>
       </c>
       <c r="R11" t="n">
-        <v>6777118</v>
+        <v>6776957</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,6 +1686,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1701,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129195306</v>
+        <v>129195296</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1712,31 +1716,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1744,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442828</v>
+        <v>442804</v>
       </c>
       <c r="R12" t="n">
-        <v>6777062</v>
+        <v>6777066</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,6 +1787,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1806,54 +1806,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129195336</v>
+        <v>129195294</v>
       </c>
       <c r="B13" t="n">
-        <v>5177</v>
+        <v>79660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442750</v>
+        <v>442435</v>
       </c>
       <c r="R13" t="n">
-        <v>6777113</v>
+        <v>6776960</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,7 +1885,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1913,45 +1903,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129195321</v>
+        <v>129195336</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>5177</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442695</v>
+        <v>442750</v>
       </c>
       <c r="R14" t="n">
-        <v>6777083</v>
+        <v>6777113</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1992,6 +1991,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129195294</v>
+        <v>129195321</v>
       </c>
       <c r="B15" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,21 +2021,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442435</v>
+        <v>442695</v>
       </c>
       <c r="R15" t="n">
-        <v>6776960</v>
+        <v>6777083</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3526,7 +3526,7 @@
         <v>129195333</v>
       </c>
       <c r="B30" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>129195332</v>
       </c>
       <c r="B32" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 15738-2025 artfynd.xlsx
+++ b/artfynd/A 15738-2025 artfynd.xlsx
@@ -1289,42 +1289,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129195309</v>
+        <v>129195331</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>92822</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1332,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442643</v>
+        <v>442474</v>
       </c>
       <c r="R8" t="n">
-        <v>6777058</v>
+        <v>6776957</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1376,6 +1371,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1394,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129195303</v>
+        <v>129195296</v>
       </c>
       <c r="B9" t="n">
-        <v>57724</v>
+        <v>91540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,31 +1401,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1437,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442807</v>
+        <v>442804</v>
       </c>
       <c r="R9" t="n">
-        <v>6777118</v>
+        <v>6777066</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,6 +1472,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1499,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129195306</v>
+        <v>129195309</v>
       </c>
       <c r="B10" t="n">
         <v>57724</v>
@@ -1542,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442828</v>
+        <v>442643</v>
       </c>
       <c r="R10" t="n">
-        <v>6777062</v>
+        <v>6777058</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,37 +1596,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129195331</v>
+        <v>129195303</v>
       </c>
       <c r="B11" t="n">
-        <v>92821</v>
+        <v>57724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1642,10 +1639,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442474</v>
+        <v>442807</v>
       </c>
       <c r="R11" t="n">
-        <v>6776957</v>
+        <v>6777118</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1686,7 +1683,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1705,10 +1701,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129195296</v>
+        <v>129195306</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,26 +1712,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1743,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442804</v>
+        <v>442828</v>
       </c>
       <c r="R12" t="n">
-        <v>6777066</v>
+        <v>6777062</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1787,7 +1788,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129195312</v>
+        <v>129195298</v>
       </c>
       <c r="B25" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,21 +3017,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442510</v>
+        <v>442628</v>
       </c>
       <c r="R25" t="n">
-        <v>6776988</v>
+        <v>6777045</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129195308</v>
+        <v>129195312</v>
       </c>
       <c r="B26" t="n">
         <v>57724</v>
@@ -3144,7 +3144,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442733</v>
+        <v>442510</v>
       </c>
       <c r="R26" t="n">
-        <v>6777012</v>
+        <v>6776988</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129195298</v>
+        <v>129195308</v>
       </c>
       <c r="B27" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3249,7 +3249,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442628</v>
+        <v>442733</v>
       </c>
       <c r="R27" t="n">
-        <v>6777045</v>
+        <v>6777012</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3526,7 +3526,7 @@
         <v>129195333</v>
       </c>
       <c r="B30" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>129195332</v>
       </c>
       <c r="B32" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 15738-2025 artfynd.xlsx
+++ b/artfynd/A 15738-2025 artfynd.xlsx
@@ -1289,32 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129195331</v>
+        <v>129195296</v>
       </c>
       <c r="B8" t="n">
-        <v>92822</v>
+        <v>91540</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442474</v>
+        <v>442804</v>
       </c>
       <c r="R8" t="n">
-        <v>6776957</v>
+        <v>6777066</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,32 +1390,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129195296</v>
+        <v>129195331</v>
       </c>
       <c r="B9" t="n">
-        <v>91540</v>
+        <v>92822</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442804</v>
+        <v>442474</v>
       </c>
       <c r="R9" t="n">
-        <v>6777066</v>
+        <v>6776957</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1806,45 +1806,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129195294</v>
+        <v>129195336</v>
       </c>
       <c r="B13" t="n">
-        <v>79660</v>
+        <v>5177</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442435</v>
+        <v>442750</v>
       </c>
       <c r="R13" t="n">
-        <v>6776960</v>
+        <v>6777113</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,6 +1894,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1903,54 +1913,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129195336</v>
+        <v>129195321</v>
       </c>
       <c r="B14" t="n">
-        <v>5177</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442750</v>
+        <v>442695</v>
       </c>
       <c r="R14" t="n">
-        <v>6777113</v>
+        <v>6777083</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1991,7 +1992,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2010,10 +2010,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129195321</v>
+        <v>129195294</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,21 +2021,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2045,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442695</v>
+        <v>442435</v>
       </c>
       <c r="R15" t="n">
-        <v>6777083</v>
+        <v>6776960</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -3006,10 +3006,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129195298</v>
+        <v>129195312</v>
       </c>
       <c r="B25" t="n">
-        <v>57887</v>
+        <v>57724</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,21 +3017,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3039,7 +3039,7 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -3049,10 +3049,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442628</v>
+        <v>442510</v>
       </c>
       <c r="R25" t="n">
-        <v>6777045</v>
+        <v>6776988</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129195312</v>
+        <v>129195308</v>
       </c>
       <c r="B26" t="n">
         <v>57724</v>
@@ -3144,7 +3144,7 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442510</v>
+        <v>442733</v>
       </c>
       <c r="R26" t="n">
-        <v>6776988</v>
+        <v>6777012</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3216,10 +3216,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129195308</v>
+        <v>129195298</v>
       </c>
       <c r="B27" t="n">
-        <v>57724</v>
+        <v>57887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,21 +3227,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3249,7 +3249,7 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442733</v>
+        <v>442628</v>
       </c>
       <c r="R27" t="n">
-        <v>6777012</v>
+        <v>6777045</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 15738-2025 artfynd.xlsx
+++ b/artfynd/A 15738-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129195335</v>
       </c>
       <c r="B2" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>129195334</v>
       </c>
       <c r="B6" t="n">
-        <v>88940</v>
+        <v>88943</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>129195319</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129195296</v>
+        <v>129195309</v>
       </c>
       <c r="B8" t="n">
-        <v>91540</v>
+        <v>57724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1300,26 +1300,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1327,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442804</v>
+        <v>442643</v>
       </c>
       <c r="R8" t="n">
-        <v>6777066</v>
+        <v>6777058</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,7 +1376,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1390,37 +1394,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129195331</v>
+        <v>129195303</v>
       </c>
       <c r="B9" t="n">
-        <v>92822</v>
+        <v>57724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1428,10 +1437,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442474</v>
+        <v>442807</v>
       </c>
       <c r="R9" t="n">
-        <v>6776957</v>
+        <v>6777118</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,7 +1481,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,7 +1499,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129195309</v>
+        <v>129195306</v>
       </c>
       <c r="B10" t="n">
         <v>57724</v>
@@ -1534,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442643</v>
+        <v>442828</v>
       </c>
       <c r="R10" t="n">
-        <v>6777058</v>
+        <v>6777062</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1596,10 +1604,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129195303</v>
+        <v>129195296</v>
       </c>
       <c r="B11" t="n">
-        <v>57724</v>
+        <v>91543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1607,31 +1615,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1639,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442807</v>
+        <v>442804</v>
       </c>
       <c r="R11" t="n">
-        <v>6777118</v>
+        <v>6777066</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1683,6 +1686,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1701,42 +1705,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129195306</v>
+        <v>129195331</v>
       </c>
       <c r="B12" t="n">
-        <v>57724</v>
+        <v>92825</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1744,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442828</v>
+        <v>442474</v>
       </c>
       <c r="R12" t="n">
-        <v>6777062</v>
+        <v>6776957</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1788,6 +1787,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1806,54 +1806,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129195336</v>
+        <v>129195321</v>
       </c>
       <c r="B13" t="n">
-        <v>5177</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442750</v>
+        <v>442695</v>
       </c>
       <c r="R13" t="n">
-        <v>6777113</v>
+        <v>6777083</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1894,7 +1885,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1913,10 +1903,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129195321</v>
+        <v>129195294</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,21 +1914,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1948,10 +1938,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442695</v>
+        <v>442435</v>
       </c>
       <c r="R14" t="n">
-        <v>6777083</v>
+        <v>6776960</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,45 +2000,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129195294</v>
+        <v>129195336</v>
       </c>
       <c r="B15" t="n">
-        <v>79660</v>
+        <v>5177</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Digerås, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442435</v>
+        <v>442750</v>
       </c>
       <c r="R15" t="n">
-        <v>6776960</v>
+        <v>6777113</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2089,6 +2088,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>129195329</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>129195322</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
         <v>129195327</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>129195330</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>129195320</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2912,7 +2912,7 @@
         <v>129195324</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>129195326</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>129195333</v>
       </c>
       <c r="B30" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         <v>129195325</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>129195332</v>
       </c>
       <c r="B32" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         <v>129195328</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 15738-2025 artfynd.xlsx
+++ b/artfynd/A 15738-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195331</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195332</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195333</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195318</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195319</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195320</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195321</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195325</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195326</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1654,6 +1704,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195327</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1755,6 +1810,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195328</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1852,6 +1912,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195329</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1949,6 +2014,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195330</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2046,6 +2116,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195294</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2151,6 +2226,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195301</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2256,6 +2336,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195309</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2361,6 +2446,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195310</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2466,6 +2556,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195311</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2571,6 +2666,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195312</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2676,6 +2776,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195313</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2781,6 +2886,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195314</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2886,6 +2996,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195298</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2993,6 +3108,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195315</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3094,6 +3214,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195334</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3195,6 +3320,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195335</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3296,6 +3426,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195296</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3393,6 +3528,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195322</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3494,6 +3634,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195323</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3591,6 +3736,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195324</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3696,6 +3846,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195302</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3801,6 +3956,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195303</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3906,6 +4066,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195304</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4011,6 +4176,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195305</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4116,6 +4286,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195306</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4221,6 +4396,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195307</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4326,6 +4506,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195308</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4431,6 +4616,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195297</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4538,8 +4728,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129195336</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>